--- a/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
+++ b/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff Rissman\CodeRepositories\eps-us\InputData\trans\VSbS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\TX\trans\VSbS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7C4D67-74A1-4BF9-A001-F474636F2E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC7A9175-4F3A-4FA6-A9A8-53C670BAD3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="2445" windowWidth="29940" windowHeight="20805" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
+    <workbookView xWindow="2340" yWindow="1110" windowWidth="13035" windowHeight="16890" firstSheet="2" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="109">
   <si>
     <t>VSbS Vehicle Shares by Subregion</t>
   </si>
@@ -380,6 +380,9 @@
   </si>
   <si>
     <t>U.S. Data Notes</t>
+  </si>
+  <si>
+    <t>Texas</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1078,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="37" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
@@ -1244,6 +1247,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1274,11 +1280,6 @@
     <xf numFmtId="37" fontId="5" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma 2" xfId="5" xr:uid="{7B2DBB66-964B-4992-8A85-CF7563C0181E}"/>
@@ -1289,147 +1290,7 @@
     <cellStyle name="Normal 5" xfId="6" xr:uid="{58A5829F-0798-4AC5-A887-3CBCA8BB0153}"/>
     <cellStyle name="Normal 8 2" xfId="4" xr:uid="{1E08BF75-563B-4006-9FB0-94126509CFF1}"/>
   </cellStyles>
-  <dxfs count="34">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1770,18 +1631,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B0F8C0-DE1A-4000-9351-A11EE8CD5BC4}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="70.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="B1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="104">
+        <v>45258</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1789,54 +1656,51 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3">
       <c r="B4" s="3">
         <v>2022</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:3">
       <c r="B5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:3">
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:3">
       <c r="B7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="112" t="s">
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="112" t="s">
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="112"/>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="113" t="s">
+    <row r="13" spans="1:3">
+      <c r="A13" s="102" t="s">
         <v>107</v>
       </c>
-      <c r="B13" s="114"/>
-    </row>
-    <row r="14" spans="1:2" s="116" customFormat="1">
-      <c r="A14" s="115"/>
-    </row>
-    <row r="15" spans="1:2">
+      <c r="B13" s="103"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1"/>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>87</v>
       </c>
@@ -1902,24 +1766,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="106" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="98"/>
@@ -1963,51 +1827,51 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="94"/>
-      <c r="B4" s="104" t="s">
+      <c r="B4" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="105"/>
-      <c r="M4" s="105"/>
-      <c r="N4" s="105"/>
-      <c r="O4" s="105"/>
-      <c r="P4" s="106"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="108"/>
+      <c r="L4" s="108"/>
+      <c r="M4" s="108"/>
+      <c r="N4" s="108"/>
+      <c r="O4" s="108"/>
+      <c r="P4" s="109"/>
     </row>
     <row r="5" spans="1:16" ht="9">
       <c r="A5" s="79"/>
-      <c r="B5" s="107" t="s">
+      <c r="B5" s="110" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="109" t="s">
+      <c r="C5" s="111"/>
+      <c r="D5" s="111"/>
+      <c r="E5" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="F5" s="108"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="108" t="s">
+      <c r="F5" s="111"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="111" t="s">
         <v>71</v>
       </c>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="109" t="s">
+      <c r="I5" s="111"/>
+      <c r="J5" s="111"/>
+      <c r="K5" s="112" t="s">
         <v>70</v>
       </c>
-      <c r="L5" s="108"/>
-      <c r="M5" s="110"/>
-      <c r="N5" s="108" t="s">
+      <c r="L5" s="111"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="111" t="s">
         <v>69</v>
       </c>
-      <c r="O5" s="108"/>
-      <c r="P5" s="111"/>
+      <c r="O5" s="111"/>
+      <c r="P5" s="114"/>
     </row>
     <row r="6" spans="1:16" ht="9">
       <c r="A6" s="79" t="s">
@@ -4790,24 +4654,24 @@
       <c r="P62" s="5"/>
     </row>
     <row r="63" spans="1:16" ht="39.6" customHeight="1">
-      <c r="A63" s="102" t="s">
+      <c r="A63" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="B63" s="102"/>
-      <c r="C63" s="102"/>
-      <c r="D63" s="102"/>
-      <c r="E63" s="102"/>
-      <c r="F63" s="102"/>
-      <c r="G63" s="102"/>
-      <c r="H63" s="102"/>
-      <c r="I63" s="102"/>
-      <c r="J63" s="102"/>
-      <c r="K63" s="102"/>
-      <c r="L63" s="102"/>
-      <c r="M63" s="102"/>
-      <c r="N63" s="102"/>
-      <c r="O63" s="102"/>
-      <c r="P63" s="102"/>
+      <c r="B63" s="105"/>
+      <c r="C63" s="105"/>
+      <c r="D63" s="105"/>
+      <c r="E63" s="105"/>
+      <c r="F63" s="105"/>
+      <c r="G63" s="105"/>
+      <c r="H63" s="105"/>
+      <c r="I63" s="105"/>
+      <c r="J63" s="105"/>
+      <c r="K63" s="105"/>
+      <c r="L63" s="105"/>
+      <c r="M63" s="105"/>
+      <c r="N63" s="105"/>
+      <c r="O63" s="105"/>
+      <c r="P63" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4820,172 +4684,32 @@
     <mergeCell ref="K5:M5"/>
     <mergeCell ref="N5:P5"/>
   </mergeCells>
-  <conditionalFormatting sqref="B11:D12 N11:P12 B34:D34 B31:B33 O34:P34 N59:P59 B59:D59 B58 B60 N19:P25 B22:D25 B10 N14:P16 B14:D16 B13 B17 B30:D30 N30:P30 B28 O36:P37 B36:D37 B35 B40:D50 O40:P50 B38:B39 B27:D27 B26 N27:P27 O52:P57 B52:D57 B51 C19:D21 G52:K57 G27:K27 G40:K50 G36:K37 G30:K30 G14:K16 G19:K25 G59:K59 G34:K34 G11:K12">
-    <cfRule type="cellIs" dxfId="33" priority="34" operator="lessThan">
+  <conditionalFormatting sqref="B28">
+    <cfRule type="cellIs" dxfId="5" priority="34" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M11:M12 M34 M59 M19:M25 M14:M16 M30 M36:M37 M40:M50 M27 M52:M57">
-    <cfRule type="cellIs" dxfId="32" priority="33" operator="lessThan">
+  <conditionalFormatting sqref="B11:D27">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L11:L12 L34 L59 L19:L25 L14:L16 L30 L36:L37 L40:L50 L27 L52:L57">
-    <cfRule type="cellIs" dxfId="31" priority="32" operator="lessThan">
+  <conditionalFormatting sqref="B30:D60">
+    <cfRule type="cellIs" dxfId="3" priority="15" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C31">
-    <cfRule type="cellIs" dxfId="30" priority="31" operator="lessThan">
+  <conditionalFormatting sqref="B10:E10 E11:E62">
+    <cfRule type="cellIs" dxfId="2" priority="25" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D31 G31:P31">
-    <cfRule type="cellIs" dxfId="29" priority="30" operator="lessThan">
+  <conditionalFormatting sqref="C28:D29">
+    <cfRule type="cellIs" dxfId="1" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C33:D33 G33:P33">
-    <cfRule type="cellIs" dxfId="28" priority="29" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C58:D58 G58:P58">
-    <cfRule type="cellIs" dxfId="27" priority="28" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C60:D60 G60:P60">
-    <cfRule type="cellIs" dxfId="26" priority="27" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C17:D17 G17:P17">
-    <cfRule type="cellIs" dxfId="25" priority="26" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C10:E10 G10:P10 E11:E62">
-    <cfRule type="cellIs" dxfId="24" priority="25" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C13:D13 G13:O13">
-    <cfRule type="cellIs" dxfId="23" priority="24" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C18:D18 G18:P18">
-    <cfRule type="cellIs" dxfId="22" priority="23" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C28:D28 G28:P28">
-    <cfRule type="cellIs" dxfId="21" priority="22" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C29:D29 G29:P29">
-    <cfRule type="cellIs" dxfId="20" priority="21" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C35:D35 O35:P35 G35:M35">
-    <cfRule type="cellIs" dxfId="19" priority="20" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C38:D38 O38:P38 G38:M38">
-    <cfRule type="cellIs" dxfId="18" priority="19" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C39:D39 O39:P39 G39:M39">
-    <cfRule type="cellIs" dxfId="17" priority="18" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C32:D32 G32:P32">
-    <cfRule type="cellIs" dxfId="16" priority="17" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C26:D26 G26:P26">
-    <cfRule type="cellIs" dxfId="15" priority="16" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C51:D51 O51:P51 G51:M51">
-    <cfRule type="cellIs" dxfId="14" priority="15" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P13">
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N35:N36 N43:N49 N38:N40 N54 N51">
-    <cfRule type="cellIs" dxfId="12" priority="13" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N55">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N57">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N41">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N34">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N37">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N42">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N52">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N53">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N56">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N50">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B18:B21">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10:F60">
+  <conditionalFormatting sqref="F10:P60">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -5035,25 +4759,22 @@
         <v>58</v>
       </c>
       <c r="B2">
-        <f>'Table MV-1'!D10/'Table MV-1'!$D$61</f>
-        <v>1.9359587122498342E-2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <f>'Table MV-1'!G10/'Table MV-1'!$G$61</f>
-        <v>5.5878521842202787E-3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <f>'Table MV-1'!M10/'Table MV-1'!$M$61</f>
-        <v>1.3796718114729099E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -5061,12 +4782,10 @@
         <v>57</v>
       </c>
       <c r="B3">
-        <f>'Table MV-1'!D11/'Table MV-1'!$D$61</f>
-        <v>1.6278452622477892E-3</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <f>'Table MV-1'!G11/'Table MV-1'!$G$61</f>
-        <v>8.5645956308639404E-3</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -5078,8 +4797,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <f>'Table MV-1'!M11/'Table MV-1'!$M$61</f>
-        <v>3.2157240392212427E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -5087,12 +4805,10 @@
         <v>56</v>
       </c>
       <c r="B4">
-        <f>'Table MV-1'!D12/'Table MV-1'!$D$61</f>
-        <v>2.2923014439488926E-2</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <f>'Table MV-1'!G12/'Table MV-1'!$G$61</f>
-        <v>8.4314569052797456E-3</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -5104,8 +4820,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <f>'Table MV-1'!M12/'Table MV-1'!$M$61</f>
-        <v>1.4537940044235568E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5113,12 +4828,10 @@
         <v>55</v>
       </c>
       <c r="B5">
-        <f>'Table MV-1'!D13/'Table MV-1'!$D$61</f>
-        <v>8.298230946218824E-3</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <f>'Table MV-1'!G13/'Table MV-1'!$G$61</f>
-        <v>1.1966588141313841E-2</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -5130,8 +4843,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <f>'Table MV-1'!M13/'Table MV-1'!$M$61</f>
-        <v>2.0388346017237942E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -5139,12 +4851,10 @@
         <v>54</v>
       </c>
       <c r="B6">
-        <f>'Table MV-1'!D14/'Table MV-1'!$D$61</f>
-        <v>0.13507737172957132</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <f>'Table MV-1'!G14/'Table MV-1'!$G$61</f>
-        <v>0.10017993599405446</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -5156,8 +4866,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <f>'Table MV-1'!M14/'Table MV-1'!$M$61</f>
-        <v>9.4309653776233349E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -5165,12 +4874,10 @@
         <v>53</v>
       </c>
       <c r="B7">
-        <f>'Table MV-1'!D15/'Table MV-1'!$D$61</f>
-        <v>1.5589702031572649E-2</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <f>'Table MV-1'!G15/'Table MV-1'!$G$61</f>
-        <v>1.3631815783695276E-2</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -5182,8 +4889,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <f>'Table MV-1'!M15/'Table MV-1'!$M$61</f>
-        <v>2.1503721119001361E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -5191,12 +4897,10 @@
         <v>52</v>
       </c>
       <c r="B8">
-        <f>'Table MV-1'!D16/'Table MV-1'!$D$61</f>
-        <v>1.1520117410612801E-2</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <f>'Table MV-1'!G16/'Table MV-1'!$G$61</f>
-        <v>1.169732997240849E-2</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -5208,8 +4912,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <f>'Table MV-1'!M16/'Table MV-1'!$M$61</f>
-        <v>9.7199374650282049E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -5217,12 +4920,10 @@
         <v>51</v>
       </c>
       <c r="B9">
-        <f>'Table MV-1'!D17/'Table MV-1'!$D$61</f>
-        <v>3.955997652548668E-3</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <f>'Table MV-1'!G17/'Table MV-1'!$G$61</f>
-        <v>3.8341965823090428E-3</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -5234,8 +4935,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <f>'Table MV-1'!M17/'Table MV-1'!$M$61</f>
-        <v>4.8306104364239793E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5243,12 +4943,10 @@
         <v>84</v>
       </c>
       <c r="B10">
-        <f>'Table MV-1'!D18/'Table MV-1'!$D$61</f>
-        <v>2.0002511050046939E-3</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <f>'Table MV-1'!G18/'Table MV-1'!$G$61</f>
-        <v>5.1000080479378894E-3</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -5260,8 +4958,7 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <f>'Table MV-1'!M18/'Table MV-1'!$M$61</f>
-        <v>4.2830692087308811E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -5269,12 +4966,10 @@
         <v>49</v>
       </c>
       <c r="B11">
-        <f>'Table MV-1'!D19/'Table MV-1'!$D$61</f>
-        <v>7.4585348593669304E-2</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <f>'Table MV-1'!G19/'Table MV-1'!$G$61</f>
-        <v>5.9786242795356839E-2</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -5286,8 +4981,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <f>'Table MV-1'!M19/'Table MV-1'!$M$61</f>
-        <v>7.4455640755318714E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -5295,12 +4989,10 @@
         <v>48</v>
       </c>
       <c r="B12">
-        <f>'Table MV-1'!D20/'Table MV-1'!$D$61</f>
-        <v>3.3246882826224872E-2</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <f>'Table MV-1'!G20/'Table MV-1'!$G$61</f>
-        <v>3.6664815309761158E-2</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -5312,8 +5004,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <f>'Table MV-1'!M20/'Table MV-1'!$M$61</f>
-        <v>2.4934379105058271E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5321,12 +5012,10 @@
         <v>47</v>
       </c>
       <c r="B13">
-        <f>'Table MV-1'!D21/'Table MV-1'!$D$61</f>
-        <v>4.5177880312321358E-3</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <f>'Table MV-1'!G21/'Table MV-1'!$G$61</f>
-        <v>2.8664568903761568E-3</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -5338,8 +5027,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <f>'Table MV-1'!M21/'Table MV-1'!$M$61</f>
-        <v>4.4403672368620124E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -5347,12 +5035,10 @@
         <v>46</v>
       </c>
       <c r="B14">
-        <f>'Table MV-1'!D22/'Table MV-1'!$D$61</f>
-        <v>5.5962364686266176E-3</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <f>'Table MV-1'!G22/'Table MV-1'!$G$61</f>
-        <v>3.782530808201743E-3</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -5364,8 +5050,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <f>'Table MV-1'!M22/'Table MV-1'!$M$61</f>
-        <v>7.1114318443253836E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -5373,12 +5058,10 @@
         <v>45</v>
       </c>
       <c r="B15">
-        <f>'Table MV-1'!D23/'Table MV-1'!$D$61</f>
-        <v>3.9583802966272987E-2</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <f>'Table MV-1'!G23/'Table MV-1'!$G$61</f>
-        <v>3.2598122743969261E-2</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -5390,8 +5073,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <f>'Table MV-1'!M23/'Table MV-1'!$M$61</f>
-        <v>3.3659616673110682E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -5399,12 +5081,10 @@
         <v>44</v>
       </c>
       <c r="B16">
-        <f>'Table MV-1'!D24/'Table MV-1'!$D$61</f>
-        <v>2.0200142102604929E-2</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <f>'Table MV-1'!G24/'Table MV-1'!$G$61</f>
-        <v>2.0735859723449008E-2</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -5416,8 +5096,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <f>'Table MV-1'!M24/'Table MV-1'!$M$61</f>
-        <v>2.519458126304313E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -5425,12 +5104,10 @@
         <v>43</v>
       </c>
       <c r="B17">
-        <f>'Table MV-1'!D25/'Table MV-1'!$D$61</f>
-        <v>1.1069079557484499E-2</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <f>'Table MV-1'!G25/'Table MV-1'!$G$61</f>
-        <v>9.1140412670434948E-3</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -5442,8 +5119,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <f>'Table MV-1'!M25/'Table MV-1'!$M$61</f>
-        <v>2.3030832815010314E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -5451,12 +5127,10 @@
         <v>42</v>
       </c>
       <c r="B18">
-        <f>'Table MV-1'!D26/'Table MV-1'!$D$61</f>
-        <v>8.4565602609209273E-3</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <f>'Table MV-1'!G26/'Table MV-1'!$G$61</f>
-        <v>6.5585725938901249E-3</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -5468,8 +5142,7 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <f>'Table MV-1'!M26/'Table MV-1'!$M$61</f>
-        <v>1.0883942873198577E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -5477,12 +5150,10 @@
         <v>41</v>
       </c>
       <c r="B19">
-        <f>'Table MV-1'!D27/'Table MV-1'!$D$61</f>
-        <v>1.5641720716067772E-2</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <f>'Table MV-1'!G27/'Table MV-1'!$G$61</f>
-        <v>1.0917375497904058E-2</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -5494,8 +5165,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <f>'Table MV-1'!M27/'Table MV-1'!$M$61</f>
-        <v>1.166599024512076E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -5503,12 +5173,10 @@
         <v>40</v>
       </c>
       <c r="B20">
-        <f>'Table MV-1'!D28/'Table MV-1'!$D$61</f>
-        <v>1.2514264951923855E-2</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <f>'Table MV-1'!G28/'Table MV-1'!$G$61</f>
-        <v>2.9889643893651965E-2</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -5520,8 +5188,7 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <f>'Table MV-1'!M28/'Table MV-1'!$M$61</f>
-        <v>1.2186394561090472E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -5529,12 +5196,10 @@
         <v>39</v>
       </c>
       <c r="B21">
-        <f>'Table MV-1'!D29/'Table MV-1'!$D$61</f>
-        <v>3.3868643547885439E-3</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <f>'Table MV-1'!G29/'Table MV-1'!$G$61</f>
-        <v>4.5932860326547567E-3</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -5546,8 +5211,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <f>'Table MV-1'!M29/'Table MV-1'!$M$61</f>
-        <v>4.6036690065248661E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -5555,12 +5219,10 @@
         <v>38</v>
       </c>
       <c r="B22">
-        <f>'Table MV-1'!D30/'Table MV-1'!$D$61</f>
-        <v>1.7344821387298082E-2</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <f>'Table MV-1'!G30/'Table MV-1'!$G$61</f>
-        <v>2.2395125930356523E-2</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -5572,8 +5234,7 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <f>'Table MV-1'!M30/'Table MV-1'!$M$61</f>
-        <v>1.3514422187907504E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -5581,12 +5242,10 @@
         <v>83</v>
       </c>
       <c r="B23">
-        <f>'Table MV-1'!D31/'Table MV-1'!$D$61</f>
-        <v>1.9055188885179382E-2</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <f>'Table MV-1'!G31/'Table MV-1'!$G$61</f>
-        <v>1.3663610106222844E-2</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -5598,8 +5257,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <f>'Table MV-1'!M31/'Table MV-1'!$M$61</f>
-        <v>1.6585095831722331E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -5607,12 +5265,10 @@
         <v>36</v>
       </c>
       <c r="B24">
-        <f>'Table MV-1'!D32/'Table MV-1'!$D$61</f>
-        <v>2.5602285816466973E-2</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <f>'Table MV-1'!G32/'Table MV-1'!$G$61</f>
-        <v>8.8845260012976063E-3</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -5624,8 +5280,7 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <f>'Table MV-1'!M32/'Table MV-1'!$M$61</f>
-        <v>2.8515490853900149E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -5633,12 +5288,10 @@
         <v>35</v>
       </c>
       <c r="B25">
-        <f>'Table MV-1'!D33/'Table MV-1'!$D$61</f>
-        <v>1.7517332427833467E-2</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <f>'Table MV-1'!G33/'Table MV-1'!$G$61</f>
-        <v>1.9068644935909602E-2</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -5650,8 +5303,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <f>'Table MV-1'!M33/'Table MV-1'!$M$61</f>
-        <v>2.9294896579548375E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -5659,12 +5311,10 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <f>'Table MV-1'!D34/'Table MV-1'!$D$61</f>
-        <v>7.4991463380995726E-3</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <f>'Table MV-1'!G34/'Table MV-1'!$G$61</f>
-        <v>7.3385270683945557E-3</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -5676,8 +5326,7 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <f>'Table MV-1'!M34/'Table MV-1'!$M$61</f>
-        <v>3.6710477969870824E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -5685,12 +5334,10 @@
         <v>33</v>
       </c>
       <c r="B27">
-        <f>'Table MV-1'!D35/'Table MV-1'!$D$61</f>
-        <v>1.8941078781341755E-2</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <f>'Table MV-1'!G35/'Table MV-1'!$G$61</f>
-        <v>3.3533074540795592E-2</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -5702,8 +5349,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <f>'Table MV-1'!M35/'Table MV-1'!$M$61</f>
-        <v>1.5214201490368798E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -5711,12 +5357,10 @@
         <v>32</v>
       </c>
       <c r="B28">
-        <f>'Table MV-1'!D36/'Table MV-1'!$D$61</f>
-        <v>4.3665733583296952E-3</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <f>'Table MV-1'!G36/'Table MV-1'!$G$61</f>
-        <v>5.1616095478350553E-3</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -5728,8 +5372,7 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <f>'Table MV-1'!M36/'Table MV-1'!$M$61</f>
-        <v>4.2647577970591273E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -5737,12 +5380,10 @@
         <v>31</v>
       </c>
       <c r="B29">
-        <f>'Table MV-1'!D37/'Table MV-1'!$D$61</f>
-        <v>5.9438361806167864E-3</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <f>'Table MV-1'!G37/'Table MV-1'!$G$61</f>
-        <v>1.7177876318098223E-2</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -5754,8 +5395,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <f>'Table MV-1'!M37/'Table MV-1'!$M$61</f>
-        <v>6.0485294435492195E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -5763,12 +5403,10 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <f>'Table MV-1'!D38/'Table MV-1'!$D$61</f>
-        <v>9.7731494559867137E-3</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <f>'Table MV-1'!G38/'Table MV-1'!$G$61</f>
-        <v>3.1883744059677944E-3</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -5780,8 +5418,7 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <f>'Table MV-1'!M38/'Table MV-1'!$M$61</f>
-        <v>8.327909953483011E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -5789,12 +5426,10 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <f>'Table MV-1'!D39/'Table MV-1'!$D$61</f>
-        <v>4.3831615071246288E-3</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <f>'Table MV-1'!G39/'Table MV-1'!$G$61</f>
-        <v>3.0602035432785312E-3</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -5806,8 +5441,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <f>'Table MV-1'!M39/'Table MV-1'!$M$61</f>
-        <v>9.4484482729637106E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -5815,12 +5449,10 @@
         <v>28</v>
       </c>
       <c r="B32">
-        <f>'Table MV-1'!D40/'Table MV-1'!$D$61</f>
-        <v>2.4170045645943845E-2</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <f>'Table MV-1'!G40/'Table MV-1'!$G$61</f>
-        <v>2.5791157005332504E-2</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -5832,8 +5464,7 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <f>'Table MV-1'!M40/'Table MV-1'!$M$61</f>
-        <v>1.4574562867579076E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -5841,12 +5472,10 @@
         <v>27</v>
       </c>
       <c r="B33">
-        <f>'Table MV-1'!D41/'Table MV-1'!$D$61</f>
-        <v>5.9347811819626707E-3</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <f>'Table MV-1'!G41/'Table MV-1'!$G$61</f>
-        <v>9.7280691208571756E-3</v>
+        <v>0</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -5858,8 +5487,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <f>'Table MV-1'!M41/'Table MV-1'!$M$61</f>
-        <v>6.5976316440405662E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -5867,12 +5495,10 @@
         <v>26</v>
       </c>
       <c r="B34">
-        <f>'Table MV-1'!D42/'Table MV-1'!$D$61</f>
-        <v>4.0260007818496736E-2</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <f>'Table MV-1'!G42/'Table MV-1'!$G$61</f>
-        <v>8.1156995396778245E-2</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -5884,8 +5510,7 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <f>'Table MV-1'!M42/'Table MV-1'!$M$61</f>
-        <v>4.6183181358622691E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -5893,12 +5518,10 @@
         <v>25</v>
       </c>
       <c r="B35">
-        <f>'Table MV-1'!D43/'Table MV-1'!$D$61</f>
-        <v>3.232472823114596E-2</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <f>'Table MV-1'!G43/'Table MV-1'!$G$61</f>
-        <v>3.311776120277922E-2</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -5910,8 +5533,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <f>'Table MV-1'!M43/'Table MV-1'!$M$61</f>
-        <v>2.2775793874742739E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -5919,12 +5541,10 @@
         <v>24</v>
       </c>
       <c r="B36">
-        <f>'Table MV-1'!D44/'Table MV-1'!$D$61</f>
-        <v>2.0512044955405084E-3</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <f>'Table MV-1'!G44/'Table MV-1'!$G$61</f>
-        <v>3.6394563568276817E-3</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -5936,8 +5556,7 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <f>'Table MV-1'!M44/'Table MV-1'!$M$61</f>
-        <v>4.3507914132087117E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -5945,12 +5564,10 @@
         <v>23</v>
       </c>
       <c r="B37">
-        <f>'Table MV-1'!D45/'Table MV-1'!$D$61</f>
-        <v>4.0403584714173067E-2</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <f>'Table MV-1'!G45/'Table MV-1'!$G$61</f>
-        <v>4.1215377721519487E-2</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -5962,8 +5579,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <f>'Table MV-1'!M45/'Table MV-1'!$M$61</f>
-        <v>4.5702521811592983E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -5971,12 +5587,10 @@
         <v>22</v>
       </c>
       <c r="B38">
-        <f>'Table MV-1'!D46/'Table MV-1'!$D$61</f>
-        <v>1.1640695370631938E-2</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <f>'Table MV-1'!G46/'Table MV-1'!$G$61</f>
-        <v>2.8227396969007492E-3</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -5988,8 +5602,7 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <f>'Table MV-1'!M46/'Table MV-1'!$M$61</f>
-        <v>1.6077419447799869E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -5997,12 +5610,10 @@
         <v>21</v>
       </c>
       <c r="B39">
-        <f>'Table MV-1'!D47/'Table MV-1'!$D$61</f>
-        <v>1.3704702416790554E-2</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <f>'Table MV-1'!G47/'Table MV-1'!$G$61</f>
-        <v>1.772632838169879E-2</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -6014,8 +5625,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <f>'Table MV-1'!M47/'Table MV-1'!$M$61</f>
-        <v>1.4843290338538977E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -6023,12 +5633,10 @@
         <v>20</v>
       </c>
       <c r="B40">
-        <f>'Table MV-1'!D48/'Table MV-1'!$D$61</f>
-        <v>3.846201038090917E-2</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <f>'Table MV-1'!G48/'Table MV-1'!$G$61</f>
-        <v>5.4911775722848888E-2</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -6040,8 +5648,7 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <f>'Table MV-1'!M48/'Table MV-1'!$M$61</f>
-        <v>4.3286135919905287E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -6049,12 +5656,10 @@
         <v>19</v>
       </c>
       <c r="B41">
-        <f>'Table MV-1'!D49/'Table MV-1'!$D$61</f>
-        <v>3.6311971335983252E-3</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <f>'Table MV-1'!G49/'Table MV-1'!$G$61</f>
-        <v>2.3031012380907907E-3</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -6066,8 +5671,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <f>'Table MV-1'!M49/'Table MV-1'!$M$61</f>
-        <v>2.8346065267874938E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -6075,12 +5679,10 @@
         <v>18</v>
       </c>
       <c r="B42">
-        <f>'Table MV-1'!D50/'Table MV-1'!$D$61</f>
-        <v>1.6810224539236585E-2</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <f>'Table MV-1'!G50/'Table MV-1'!$G$61</f>
-        <v>1.6360166085592303E-2</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -6092,8 +5694,7 @@
         <v>0</v>
       </c>
       <c r="G42">
-        <f>'Table MV-1'!M50/'Table MV-1'!$M$61</f>
-        <v>1.3750249155273566E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -6101,12 +5702,10 @@
         <v>17</v>
       </c>
       <c r="B43">
-        <f>'Table MV-1'!D51/'Table MV-1'!$D$61</f>
-        <v>3.0912643041870807E-3</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <f>'Table MV-1'!G51/'Table MV-1'!$G$61</f>
-        <v>2.6518452133150647E-3</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -6118,8 +5717,7 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <f>'Table MV-1'!M51/'Table MV-1'!$M$61</f>
-        <v>1.5581990696602122E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -6127,12 +5725,10 @@
         <v>16</v>
       </c>
       <c r="B44">
-        <f>'Table MV-1'!D52/'Table MV-1'!$D$61</f>
-        <v>2.0122946336767956E-2</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <f>'Table MV-1'!G52/'Table MV-1'!$G$61</f>
-        <v>2.9370005434842007E-2</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -6144,8 +5740,7 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <f>'Table MV-1'!M52/'Table MV-1'!$M$61</f>
-        <v>2.12856652265692E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -6153,12 +5748,10 @@
         <v>15</v>
       </c>
       <c r="B45">
-        <f>'Table MV-1'!D53/'Table MV-1'!$D$61</f>
-        <v>7.6929994017233036E-2</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <f>'Table MV-1'!G53/'Table MV-1'!$G$61</f>
-        <v>7.0475096600093989E-2</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -6170,8 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <f>'Table MV-1'!M53/'Table MV-1'!$M$61</f>
-        <v>3.9420566897290392E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -6179,12 +5771,10 @@
         <v>14</v>
       </c>
       <c r="B46">
-        <f>'Table MV-1'!D54/'Table MV-1'!$D$61</f>
-        <v>8.5862978466794693E-3</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <f>'Table MV-1'!G54/'Table MV-1'!$G$61</f>
-        <v>6.3797295296725487E-3</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -6196,8 +5786,7 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <f>'Table MV-1'!M54/'Table MV-1'!$M$61</f>
-        <v>1.4880153311543754E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -6205,12 +5794,10 @@
         <v>13</v>
       </c>
       <c r="B47">
-        <f>'Table MV-1'!D55/'Table MV-1'!$D$61</f>
-        <v>1.8396009713198137E-3</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <f>'Table MV-1'!G55/'Table MV-1'!$G$61</f>
-        <v>1.0720648127264725E-3</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -6222,8 +5809,7 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <f>'Table MV-1'!M55/'Table MV-1'!$M$61</f>
-        <v>3.4752057482222922E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -6231,12 +5817,10 @@
         <v>12</v>
       </c>
       <c r="B48">
-        <f>'Table MV-1'!D56/'Table MV-1'!$D$61</f>
-        <v>2.9079234091689471E-2</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <f>'Table MV-1'!G56/'Table MV-1'!$G$61</f>
-        <v>3.5235064368599529E-2</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -6248,8 +5832,7 @@
         <v>0</v>
       </c>
       <c r="G48">
-        <f>'Table MV-1'!M56/'Table MV-1'!$M$61</f>
-        <v>2.2146721837048848E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -6257,12 +5840,10 @@
         <v>11</v>
       </c>
       <c r="B49">
-        <f>'Table MV-1'!D57/'Table MV-1'!$D$61</f>
-        <v>2.6635868257378827E-2</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <f>'Table MV-1'!G57/'Table MV-1'!$G$61</f>
-        <v>2.4016636379262549E-2</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -6274,8 +5855,7 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <f>'Table MV-1'!M57/'Table MV-1'!$M$61</f>
-        <v>2.6590331094337991E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -6283,12 +5863,10 @@
         <v>10</v>
       </c>
       <c r="B50">
-        <f>'Table MV-1'!D58/'Table MV-1'!$D$61</f>
-        <v>4.8381751894939189E-3</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <f>'Table MV-1'!G58/'Table MV-1'!$G$61</f>
-        <v>3.1347214867025212E-3</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -6300,8 +5878,7 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <f>'Table MV-1'!M58/'Table MV-1'!$M$61</f>
-        <v>5.2267373026870347E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -6309,12 +5886,10 @@
         <v>9</v>
       </c>
       <c r="B51">
-        <f>'Table MV-1'!D59/'Table MV-1'!$D$61</f>
-        <v>1.8086189890550556E-2</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <f>'Table MV-1'!G59/'Table MV-1'!$G$61</f>
-        <v>1.4844967902637837E-2</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -6326,8 +5901,7 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <f>'Table MV-1'!M59/'Table MV-1'!$M$61</f>
-        <v>3.3177876452605261E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -6335,12 +5909,10 @@
         <v>8</v>
       </c>
       <c r="B52">
-        <f>'Table MV-1'!D60/'Table MV-1'!$D$61</f>
-        <v>1.8198644984129973E-3</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <f>'Table MV-1'!G60/'Table MV-1'!$G$61</f>
-        <v>4.0746411464237849E-3</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -6352,8 +5924,7 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <f>'Table MV-1'!M60/'Table MV-1'!$M$61</f>
-        <v>3.420691775114251E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -6609,24 +6180,22 @@
         <v>58</v>
       </c>
       <c r="B2">
-        <f>C2</f>
-        <v>1.9600927701391289E-2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <f>'Table MV-1'!J10/'Table MV-1'!$J$61</f>
-        <v>1.9600927701391289E-2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -6634,12 +6203,10 @@
         <v>57</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B52" si="0">C3</f>
-        <v>3.6314972397001131E-3</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <f>'Table MV-1'!J11/'Table MV-1'!$J$61</f>
-        <v>3.6314972397001131E-3</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -6659,12 +6226,10 @@
         <v>56</v>
       </c>
       <c r="B4">
-        <f t="shared" si="0"/>
-        <v>2.1767409304149131E-2</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <f>'Table MV-1'!J12/'Table MV-1'!$J$61</f>
-        <v>2.1767409304149131E-2</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -6684,12 +6249,10 @@
         <v>55</v>
       </c>
       <c r="B5">
-        <f t="shared" si="0"/>
-        <v>1.1515440266444459E-2</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <f>'Table MV-1'!J13/'Table MV-1'!$J$61</f>
-        <v>1.1515440266444459E-2</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -6709,12 +6272,10 @@
         <v>54</v>
       </c>
       <c r="B6">
-        <f t="shared" si="0"/>
-        <v>9.483573703336938E-2</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <f>'Table MV-1'!J14/'Table MV-1'!$J$61</f>
-        <v>9.483573703336938E-2</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -6734,12 +6295,10 @@
         <v>53</v>
       </c>
       <c r="B7">
-        <f t="shared" si="0"/>
-        <v>2.17963420575671E-2</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <f>'Table MV-1'!J15/'Table MV-1'!$J$61</f>
-        <v>2.17963420575671E-2</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -6759,12 +6318,10 @@
         <v>52</v>
       </c>
       <c r="B8">
-        <f t="shared" si="0"/>
-        <v>9.6855101995915252E-3</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <f>'Table MV-1'!J16/'Table MV-1'!$J$61</f>
-        <v>9.6855101995915252E-3</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6784,12 +6341,10 @@
         <v>51</v>
       </c>
       <c r="B9">
-        <f t="shared" si="0"/>
-        <v>3.607073808587494E-3</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <f>'Table MV-1'!J17/'Table MV-1'!$J$61</f>
-        <v>3.607073808587494E-3</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -6809,12 +6364,10 @@
         <v>84</v>
       </c>
       <c r="B10">
-        <f t="shared" si="0"/>
-        <v>8.5193982126037439E-4</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <f>'Table MV-1'!J18/'Table MV-1'!$J$61</f>
-        <v>8.5193982126037439E-4</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -6834,12 +6387,10 @@
         <v>49</v>
       </c>
       <c r="B11">
-        <f t="shared" si="0"/>
-        <v>6.1586335732623156E-2</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <f>'Table MV-1'!J19/'Table MV-1'!$J$61</f>
-        <v>6.1586335732623156E-2</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6859,12 +6410,10 @@
         <v>48</v>
       </c>
       <c r="B12">
-        <f t="shared" si="0"/>
-        <v>3.1525712849526988E-2</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <f>'Table MV-1'!J20/'Table MV-1'!$J$61</f>
-        <v>3.1525712849526988E-2</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6884,12 +6433,10 @@
         <v>47</v>
       </c>
       <c r="B13">
-        <f t="shared" si="0"/>
-        <v>4.5222742187277015E-3</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <f>'Table MV-1'!J21/'Table MV-1'!$J$61</f>
-        <v>4.5222742187277015E-3</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -6909,12 +6456,10 @@
         <v>46</v>
       </c>
       <c r="B14">
-        <f t="shared" si="0"/>
-        <v>7.8435139790973586E-3</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <f>'Table MV-1'!J22/'Table MV-1'!$J$61</f>
-        <v>7.8435139790973586E-3</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -6934,12 +6479,10 @@
         <v>45</v>
       </c>
       <c r="B15">
-        <f t="shared" si="0"/>
-        <v>3.7864302450454933E-2</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <f>'Table MV-1'!J23/'Table MV-1'!$J$61</f>
-        <v>3.7864302450454933E-2</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -6959,12 +6502,10 @@
         <v>44</v>
       </c>
       <c r="B16">
-        <f t="shared" si="0"/>
-        <v>2.3819250059067168E-2</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <f>'Table MV-1'!J24/'Table MV-1'!$J$61</f>
-        <v>2.3819250059067168E-2</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -6984,12 +6525,10 @@
         <v>43</v>
       </c>
       <c r="B17">
-        <f t="shared" si="0"/>
-        <v>1.5005240724472678E-2</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <f>'Table MV-1'!J25/'Table MV-1'!$J$61</f>
-        <v>1.5005240724472678E-2</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7009,12 +6548,10 @@
         <v>42</v>
       </c>
       <c r="B18">
-        <f t="shared" si="0"/>
-        <v>1.0017236512864749E-2</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <f>'Table MV-1'!J26/'Table MV-1'!$J$61</f>
-        <v>1.0017236512864749E-2</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -7034,12 +6571,10 @@
         <v>41</v>
       </c>
       <c r="B19">
-        <f t="shared" si="0"/>
-        <v>1.6767766333459132E-2</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <f>'Table MV-1'!J27/'Table MV-1'!$J$61</f>
-        <v>1.6767766333459132E-2</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -7059,12 +6594,10 @@
         <v>40</v>
       </c>
       <c r="B20">
-        <f t="shared" si="0"/>
-        <v>1.4952243799136747E-2</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <f>'Table MV-1'!J28/'Table MV-1'!$J$61</f>
-        <v>1.4952243799136747E-2</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -7084,12 +6617,10 @@
         <v>39</v>
       </c>
       <c r="B21">
-        <f t="shared" si="0"/>
-        <v>4.472553985012004E-3</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <f>'Table MV-1'!J29/'Table MV-1'!$J$61</f>
-        <v>4.472553985012004E-3</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -7109,12 +6640,10 @@
         <v>38</v>
       </c>
       <c r="B22">
-        <f t="shared" si="0"/>
-        <v>1.3953713838208291E-2</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <f>'Table MV-1'!J30/'Table MV-1'!$J$61</f>
-        <v>1.3953713838208291E-2</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -7134,12 +6663,10 @@
         <v>83</v>
       </c>
       <c r="B23">
-        <f t="shared" si="0"/>
-        <v>1.7847984402303698E-2</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <f>'Table MV-1'!J31/'Table MV-1'!$J$61</f>
-        <v>1.7847984402303698E-2</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -7159,12 +6686,10 @@
         <v>36</v>
       </c>
       <c r="B24">
-        <f t="shared" si="0"/>
-        <v>3.4161287854521931E-2</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <f>'Table MV-1'!J32/'Table MV-1'!$J$61</f>
-        <v>3.4161287854521931E-2</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -7184,12 +6709,10 @@
         <v>35</v>
       </c>
       <c r="B25">
-        <f t="shared" si="0"/>
-        <v>2.221147844524117E-2</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <f>'Table MV-1'!J33/'Table MV-1'!$J$61</f>
-        <v>2.221147844524117E-2</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -7209,12 +6732,10 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <f t="shared" si="0"/>
-        <v>7.63482155174601E-3</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <f>'Table MV-1'!J34/'Table MV-1'!$J$61</f>
-        <v>7.63482155174601E-3</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -7234,12 +6755,10 @@
         <v>33</v>
       </c>
       <c r="B27">
-        <f t="shared" si="0"/>
-        <v>2.1277992980917738E-2</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <f>'Table MV-1'!J35/'Table MV-1'!$J$61</f>
-        <v>2.1277992980917738E-2</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -7259,12 +6778,10 @@
         <v>32</v>
       </c>
       <c r="B28">
-        <f t="shared" si="0"/>
-        <v>7.0185743445526595E-3</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <f>'Table MV-1'!J36/'Table MV-1'!$J$61</f>
-        <v>7.0185743445526595E-3</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -7284,12 +6801,10 @@
         <v>31</v>
       </c>
       <c r="B29">
-        <f t="shared" si="0"/>
-        <v>7.6979830346411097E-3</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <f>'Table MV-1'!J37/'Table MV-1'!$J$61</f>
-        <v>7.6979830346411097E-3</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -7309,12 +6824,10 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <f t="shared" si="0"/>
-        <v>8.9770758442244206E-3</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <f>'Table MV-1'!J38/'Table MV-1'!$J$61</f>
-        <v>8.9770758442244206E-3</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -7334,12 +6847,10 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <f t="shared" si="0"/>
-        <v>5.0478518381385203E-3</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <f>'Table MV-1'!J39/'Table MV-1'!$J$61</f>
-        <v>5.0478518381385203E-3</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -7359,12 +6870,10 @@
         <v>28</v>
       </c>
       <c r="B32">
-        <f t="shared" si="0"/>
-        <v>2.0550771847319699E-2</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <f>'Table MV-1'!J40/'Table MV-1'!$J$61</f>
-        <v>2.0550771847319699E-2</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -7384,12 +6893,10 @@
         <v>27</v>
       </c>
       <c r="B33">
-        <f t="shared" si="0"/>
-        <v>6.7792148090505171E-3</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <f>'Table MV-1'!J41/'Table MV-1'!$J$61</f>
-        <v>6.7792148090505171E-3</v>
+        <v>0</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -7409,12 +6916,10 @@
         <v>26</v>
       </c>
       <c r="B34">
-        <f t="shared" si="0"/>
-        <v>4.1040438660927506E-2</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <f>'Table MV-1'!J42/'Table MV-1'!$J$61</f>
-        <v>4.1040438660927506E-2</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -7434,12 +6939,10 @@
         <v>25</v>
       </c>
       <c r="B35">
-        <f t="shared" si="0"/>
-        <v>3.1700275653385936E-2</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <f>'Table MV-1'!J43/'Table MV-1'!$J$61</f>
-        <v>3.1700275653385936E-2</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -7459,12 +6962,10 @@
         <v>24</v>
       </c>
       <c r="B36">
-        <f t="shared" si="0"/>
-        <v>3.986117035446643E-3</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <f>'Table MV-1'!J44/'Table MV-1'!$J$61</f>
-        <v>3.986117035446643E-3</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -7484,12 +6985,10 @@
         <v>23</v>
       </c>
       <c r="B37">
-        <f t="shared" si="0"/>
-        <v>3.6683925395789657E-2</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <f>'Table MV-1'!J45/'Table MV-1'!$J$61</f>
-        <v>3.6683925395789657E-2</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -7509,12 +7008,10 @@
         <v>22</v>
       </c>
       <c r="B38">
-        <f t="shared" si="0"/>
-        <v>1.4677986568760525E-2</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <f>'Table MV-1'!J46/'Table MV-1'!$J$61</f>
-        <v>1.4677986568760525E-2</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -7534,12 +7031,10 @@
         <v>21</v>
       </c>
       <c r="B39">
-        <f t="shared" si="0"/>
-        <v>1.5566676127984676E-2</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <f>'Table MV-1'!J47/'Table MV-1'!$J$61</f>
-        <v>1.5566676127984676E-2</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -7559,12 +7054,10 @@
         <v>20</v>
       </c>
       <c r="B40">
-        <f t="shared" si="0"/>
-        <v>3.8593803021701831E-2</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <f>'Table MV-1'!J48/'Table MV-1'!$J$61</f>
-        <v>3.8593803021701831E-2</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -7584,12 +7077,10 @@
         <v>19</v>
       </c>
       <c r="B41">
-        <f t="shared" si="0"/>
-        <v>2.8426879307146095E-3</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <f>'Table MV-1'!J49/'Table MV-1'!$J$61</f>
-        <v>2.8426879307146095E-3</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -7609,12 +7100,10 @@
         <v>18</v>
       </c>
       <c r="B42">
-        <f t="shared" si="0"/>
-        <v>1.6494772704388254E-2</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <f>'Table MV-1'!J50/'Table MV-1'!$J$61</f>
-        <v>1.6494772704388254E-2</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -7634,12 +7123,10 @@
         <v>17</v>
       </c>
       <c r="B43">
-        <f t="shared" si="0"/>
-        <v>5.1835093488657516E-3</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <f>'Table MV-1'!J51/'Table MV-1'!$J$61</f>
-        <v>5.1835093488657516E-3</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -7659,12 +7146,10 @@
         <v>16</v>
       </c>
       <c r="B44">
-        <f t="shared" si="0"/>
-        <v>2.1883288976798098E-2</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <f>'Table MV-1'!J52/'Table MV-1'!$J$61</f>
-        <v>2.1883288976798098E-2</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -7684,12 +7169,10 @@
         <v>15</v>
       </c>
       <c r="B45">
-        <f t="shared" si="0"/>
-        <v>8.6297781225124395E-2</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <f>'Table MV-1'!J53/'Table MV-1'!$J$61</f>
-        <v>8.6297781225124395E-2</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -7709,12 +7192,10 @@
         <v>14</v>
       </c>
       <c r="B46">
-        <f t="shared" si="0"/>
-        <v>8.9600234207263124E-3</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <f>'Table MV-1'!J54/'Table MV-1'!$J$61</f>
-        <v>8.9600234207263124E-3</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -7734,12 +7215,10 @@
         <v>13</v>
       </c>
       <c r="B47">
-        <f t="shared" si="0"/>
-        <v>2.3814053188992734E-3</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <f>'Table MV-1'!J55/'Table MV-1'!$J$61</f>
-        <v>2.3814053188992734E-3</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -7759,12 +7238,10 @@
         <v>12</v>
       </c>
       <c r="B48">
-        <f t="shared" si="0"/>
-        <v>2.6816184066770478E-2</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <f>'Table MV-1'!J56/'Table MV-1'!$J$61</f>
-        <v>2.6816184066770478E-2</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -7784,12 +7261,10 @@
         <v>11</v>
       </c>
       <c r="B49">
-        <f t="shared" si="0"/>
-        <v>2.6086002141878541E-2</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <f>'Table MV-1'!J57/'Table MV-1'!$J$61</f>
-        <v>2.6086002141878541E-2</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -7809,12 +7284,10 @@
         <v>10</v>
       </c>
       <c r="B50">
-        <f t="shared" si="0"/>
-        <v>6.8260176103406393E-3</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <f>'Table MV-1'!J58/'Table MV-1'!$J$61</f>
-        <v>6.8260176103406393E-3</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -7834,12 +7307,10 @@
         <v>9</v>
       </c>
       <c r="B51">
-        <f t="shared" si="0"/>
-        <v>2.1205726135675299E-2</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <f>'Table MV-1'!J59/'Table MV-1'!$J$61</f>
-        <v>2.1205726135675299E-2</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -7859,12 +7330,10 @@
         <v>8</v>
       </c>
       <c r="B52">
-        <f t="shared" si="0"/>
-        <v>3.9463197884523288E-3</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <f>'Table MV-1'!J60/'Table MV-1'!$J$61</f>
-        <v>3.9463197884523288E-3</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>0</v>

--- a/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
+++ b/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\TX\trans\VSbS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathaniyer/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/TX/trans/VSbS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC7A9175-4F3A-4FA6-A9A8-53C670BAD3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADEB4806-2487-C84D-97B6-5CBD99E50762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1110" windowWidth="13035" windowHeight="16890" firstSheet="2" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="13840" windowHeight="12640" firstSheet="1" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -1632,9 +1631,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B0F8C0-DE1A-4000-9351-A11EE8CD5BC4}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="70.140625" customWidth="1"/>
+    <col min="2" max="2" width="70.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1645,7 +1644,7 @@
         <v>108</v>
       </c>
       <c r="C1" s="104">
-        <v>45258</v>
+        <v>45295</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1758,14 +1757,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949F6402-DD66-4CAC-8910-748EA4AEB83B}">
   <dimension ref="A1:P63"/>
-  <sheetFormatPr defaultRowHeight="8.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="10"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="4" customWidth="1"/>
-    <col min="2" max="16" width="9.85546875" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="11.33203125" style="4" customWidth="1"/>
+    <col min="2" max="16" width="9.83203125" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15">
+    <row r="1" spans="1:16" ht="14">
       <c r="A1" s="106" t="s">
         <v>76</v>
       </c>
@@ -1803,7 +1802,7 @@
       <c r="O2" s="96"/>
       <c r="P2" s="96"/>
     </row>
-    <row r="3" spans="1:16" ht="9">
+    <row r="3" spans="1:16" ht="11">
       <c r="A3" s="97" t="s">
         <v>75</v>
       </c>
@@ -1845,7 +1844,7 @@
       <c r="O4" s="108"/>
       <c r="P4" s="109"/>
     </row>
-    <row r="5" spans="1:16" ht="9">
+    <row r="5" spans="1:16" ht="11">
       <c r="A5" s="79"/>
       <c r="B5" s="110" t="s">
         <v>73</v>
@@ -1873,7 +1872,7 @@
       <c r="O5" s="111"/>
       <c r="P5" s="114"/>
     </row>
-    <row r="6" spans="1:16" ht="9">
+    <row r="6" spans="1:16" ht="11">
       <c r="A6" s="79" t="s">
         <v>68</v>
       </c>
@@ -1901,7 +1900,7 @@
       <c r="O6" s="88"/>
       <c r="P6" s="87"/>
     </row>
-    <row r="7" spans="1:16" ht="9">
+    <row r="7" spans="1:16" ht="11">
       <c r="A7" s="79"/>
       <c r="B7" s="79" t="s">
         <v>63</v>
@@ -1947,7 +1946,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="9">
+    <row r="8" spans="1:16" ht="11">
       <c r="A8" s="79"/>
       <c r="B8" s="79" t="s">
         <v>65</v>
@@ -1995,7 +1994,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="9">
+    <row r="9" spans="1:16" ht="11">
       <c r="A9" s="74"/>
       <c r="B9" s="74" t="s">
         <v>60</v>
@@ -2035,7 +2034,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="9">
+    <row r="10" spans="1:16" ht="11">
       <c r="A10" s="19" t="s">
         <v>58</v>
       </c>
@@ -2085,7 +2084,7 @@
         <v>5320340</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="9">
+    <row r="11" spans="1:16" ht="11">
       <c r="A11" s="19" t="s">
         <v>57</v>
       </c>
@@ -2135,7 +2134,7 @@
         <v>792826</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="9">
+    <row r="12" spans="1:16" ht="11">
       <c r="A12" s="19" t="s">
         <v>56</v>
       </c>
@@ -2185,7 +2184,7 @@
         <v>6053781</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="9">
+    <row r="13" spans="1:16" ht="11">
       <c r="A13" s="19" t="s">
         <v>55</v>
       </c>
@@ -2235,7 +2234,7 @@
         <v>2913369</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="9">
+    <row r="14" spans="1:16" ht="11">
       <c r="A14" s="52" t="s">
         <v>54</v>
       </c>
@@ -2285,7 +2284,7 @@
         <v>30398249</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="9">
+    <row r="15" spans="1:16" ht="11">
       <c r="A15" s="19" t="s">
         <v>53</v>
       </c>
@@ -2335,7 +2334,7 @@
         <v>5350708</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="9">
+    <row r="16" spans="1:16" ht="11">
       <c r="A16" s="19" t="s">
         <v>52</v>
       </c>
@@ -2385,7 +2384,7 @@
         <v>2867554</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="9">
+    <row r="17" spans="1:16" ht="11">
       <c r="A17" s="43" t="s">
         <v>51</v>
       </c>
@@ -2435,7 +2434,7 @@
         <v>1006135</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="9">
+    <row r="18" spans="1:16" ht="11">
       <c r="A18" s="19" t="s">
         <v>50</v>
       </c>
@@ -2485,7 +2484,7 @@
         <v>356537</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="9">
+    <row r="19" spans="1:16" ht="11">
       <c r="A19" s="19" t="s">
         <v>49</v>
       </c>
@@ -2535,7 +2534,7 @@
         <v>18464506</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="9">
+    <row r="20" spans="1:16" ht="11">
       <c r="A20" s="19" t="s">
         <v>48</v>
       </c>
@@ -2585,7 +2584,7 @@
         <v>8829596</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="9">
+    <row r="21" spans="1:16" ht="11">
       <c r="A21" s="19" t="s">
         <v>47</v>
       </c>
@@ -2635,7 +2634,7 @@
         <v>1244935</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="9">
+    <row r="22" spans="1:16" ht="11">
       <c r="A22" s="52" t="s">
         <v>46</v>
       </c>
@@ -2685,7 +2684,7 @@
         <v>1917677</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="9">
+    <row r="23" spans="1:16" ht="11">
       <c r="A23" s="19" t="s">
         <v>45</v>
       </c>
@@ -2735,7 +2734,7 @@
         <v>10587725</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="9">
+    <row r="24" spans="1:16" ht="11">
       <c r="A24" s="19" t="s">
         <v>44</v>
       </c>
@@ -2785,7 +2784,7 @@
         <v>6199901</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="9">
+    <row r="25" spans="1:16" ht="11">
       <c r="A25" s="43" t="s">
         <v>43</v>
       </c>
@@ -2835,7 +2834,7 @@
         <v>3787224</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="9">
+    <row r="26" spans="1:16" ht="11">
       <c r="A26" s="19" t="s">
         <v>42</v>
       </c>
@@ -2885,7 +2884,7 @@
         <v>2603543</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="9">
+    <row r="27" spans="1:16" ht="11">
       <c r="A27" s="19" t="s">
         <v>41</v>
       </c>
@@ -2935,7 +2934,7 @@
         <v>4459685</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="9">
+    <row r="28" spans="1:16" ht="11">
       <c r="A28" s="19" t="s">
         <v>40</v>
       </c>
@@ -2985,7 +2984,7 @@
         <v>3861204</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="9">
+    <row r="29" spans="1:16" ht="11">
       <c r="A29" s="19" t="s">
         <v>39</v>
       </c>
@@ -3035,7 +3034,7 @@
         <v>1121106</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="9">
+    <row r="30" spans="1:16" ht="11">
       <c r="A30" s="52" t="s">
         <v>38</v>
       </c>
@@ -3085,7 +3084,7 @@
         <v>4211377</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="9">
+    <row r="31" spans="1:16" ht="11">
       <c r="A31" s="19" t="s">
         <v>37</v>
       </c>
@@ -3135,7 +3134,7 @@
         <v>5036686</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="9">
+    <row r="32" spans="1:16" ht="11">
       <c r="A32" s="19" t="s">
         <v>36</v>
       </c>
@@ -3185,7 +3184,7 @@
         <v>8453239</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="9">
+    <row r="33" spans="1:16" ht="11">
       <c r="A33" s="43" t="s">
         <v>35</v>
       </c>
@@ -3235,7 +3234,7 @@
         <v>5690749</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="9">
+    <row r="34" spans="1:16" ht="11">
       <c r="A34" s="19" t="s">
         <v>34</v>
       </c>
@@ -3285,7 +3284,7 @@
         <v>2058975</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="9">
+    <row r="35" spans="1:16" ht="11">
       <c r="A35" s="19" t="s">
         <v>33</v>
       </c>
@@ -3335,7 +3334,7 @@
         <v>5587022</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="9">
+    <row r="36" spans="1:16" ht="11">
       <c r="A36" s="19" t="s">
         <v>32</v>
       </c>
@@ -3385,7 +3384,7 @@
         <v>1952553</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="9">
+    <row r="37" spans="1:16" ht="11">
       <c r="A37" s="19" t="s">
         <v>31</v>
       </c>
@@ -3435,7 +3434,7 @@
         <v>1935357</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="9">
+    <row r="38" spans="1:16" ht="11">
       <c r="A38" s="52" t="s">
         <v>30</v>
       </c>
@@ -3485,7 +3484,7 @@
         <v>2549357</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="9">
+    <row r="39" spans="1:16" ht="11">
       <c r="A39" s="19" t="s">
         <v>29</v>
       </c>
@@ -3535,7 +3534,7 @@
         <v>1357535</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="9">
+    <row r="40" spans="1:16" ht="11">
       <c r="A40" s="19" t="s">
         <v>28</v>
       </c>
@@ -3585,7 +3584,7 @@
         <v>6006247</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="9">
+    <row r="41" spans="1:16" ht="11">
       <c r="A41" s="43" t="s">
         <v>27</v>
       </c>
@@ -3635,7 +3634,7 @@
         <v>1783151</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="9">
+    <row r="42" spans="1:16" ht="11">
       <c r="A42" s="19" t="s">
         <v>26</v>
       </c>
@@ -3685,7 +3684,7 @@
         <v>11324755</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="9">
+    <row r="43" spans="1:16" ht="11">
       <c r="A43" s="19" t="s">
         <v>25</v>
       </c>
@@ -3735,7 +3734,7 @@
         <v>8739280</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="9">
+    <row r="44" spans="1:16" ht="11">
       <c r="A44" s="19" t="s">
         <v>24</v>
       </c>
@@ -3785,7 +3784,7 @@
         <v>899083</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="9">
+    <row r="45" spans="1:16" ht="11">
       <c r="A45" s="19" t="s">
         <v>23</v>
       </c>
@@ -3835,7 +3834,7 @@
         <v>10592317</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="9">
+    <row r="46" spans="1:16" ht="11">
       <c r="A46" s="52" t="s">
         <v>22</v>
       </c>
@@ -3885,7 +3884,7 @@
         <v>3730247</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="9">
+    <row r="47" spans="1:16" ht="11">
       <c r="A47" s="19" t="s">
         <v>21</v>
       </c>
@@ -3935,7 +3934,7 @@
         <v>4095442</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="9">
+    <row r="48" spans="1:16" ht="11">
       <c r="A48" s="19" t="s">
         <v>20</v>
       </c>
@@ -3985,7 +3984,7 @@
         <v>10690187</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="9">
+    <row r="49" spans="1:16" ht="11">
       <c r="A49" s="43" t="s">
         <v>19</v>
       </c>
@@ -4035,7 +4034,7 @@
         <v>866625</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="9">
+    <row r="50" spans="1:16" ht="11">
       <c r="A50" s="19" t="s">
         <v>18</v>
       </c>
@@ -4085,7 +4084,7 @@
         <v>4561299</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="9">
+    <row r="51" spans="1:16" ht="11">
       <c r="A51" s="19" t="s">
         <v>17</v>
       </c>
@@ -4135,7 +4134,7 @@
         <v>1294282</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="9">
+    <row r="52" spans="1:16" ht="11">
       <c r="A52" s="19" t="s">
         <v>16</v>
       </c>
@@ -4185,7 +4184,7 @@
         <v>5855373</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="9">
+    <row r="53" spans="1:16" ht="11">
       <c r="A53" s="19" t="s">
         <v>15</v>
       </c>
@@ -4235,7 +4234,7 @@
         <v>22419490</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="9">
+    <row r="54" spans="1:16" ht="11">
       <c r="A54" s="52" t="s">
         <v>14</v>
       </c>
@@ -4285,7 +4284,7 @@
         <v>2479604</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="9">
+    <row r="55" spans="1:16" ht="11">
       <c r="A55" s="19" t="s">
         <v>13</v>
       </c>
@@ -4335,7 +4334,7 @@
         <v>607890</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="9">
+    <row r="56" spans="1:16" ht="11">
       <c r="A56" s="19" t="s">
         <v>12</v>
       </c>
@@ -4385,7 +4384,7 @@
         <v>7606452</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="9">
+    <row r="57" spans="1:16" ht="11">
       <c r="A57" s="43" t="s">
         <v>11</v>
       </c>
@@ -4435,7 +4434,7 @@
         <v>7257401</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="9">
+    <row r="58" spans="1:16" ht="11">
       <c r="A58" s="19" t="s">
         <v>10</v>
       </c>
@@ -4485,7 +4484,7 @@
         <v>1657362</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="9">
+    <row r="59" spans="1:16" ht="11">
       <c r="A59" s="19" t="s">
         <v>9</v>
       </c>
@@ -4535,7 +4534,7 @@
         <v>5616271</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="9">
+    <row r="60" spans="1:16" ht="11">
       <c r="A60" s="19" t="s">
         <v>8</v>
       </c>
@@ -4585,7 +4584,7 @@
         <v>861028</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="9">
+    <row r="61" spans="1:16" ht="11">
       <c r="A61" s="11" t="s">
         <v>7</v>
       </c>
@@ -4635,7 +4634,7 @@
         <v>275913237</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="9">
+    <row r="62" spans="1:16" ht="11">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -4653,7 +4652,7 @@
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
     </row>
-    <row r="63" spans="1:16" ht="39.6" customHeight="1">
+    <row r="63" spans="1:16" ht="39.5" customHeight="1">
       <c r="A63" s="105" t="s">
         <v>6</v>
       </c>
@@ -4725,10 +4724,10 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.7109375" customWidth="1"/>
+    <col min="2" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6146,10 +6145,10 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.7109375" customWidth="1"/>
+    <col min="2" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">

--- a/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
+++ b/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathaniyer/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/TX/trans/VSbS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\TX\trans\VSbS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADEB4806-2487-C84D-97B6-5CBD99E50762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F9E7987-2E0B-47E9-8DCE-64ED23C7FFF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="13840" windowHeight="12640" firstSheet="1" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12510" firstSheet="1" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1334,9 +1334,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1374,7 +1374,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1480,7 +1480,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1622,7 +1622,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1631,9 +1631,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B0F8C0-DE1A-4000-9351-A11EE8CD5BC4}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="70.1640625" customWidth="1"/>
+    <col min="2" max="2" width="70.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1644,7 +1644,7 @@
         <v>108</v>
       </c>
       <c r="C1" s="104">
-        <v>45295</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1757,14 +1757,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949F6402-DD66-4CAC-8910-748EA4AEB83B}">
   <dimension ref="A1:P63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="10"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="4" customWidth="1"/>
-    <col min="2" max="16" width="9.83203125" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="9.1640625" style="4"/>
+    <col min="1" max="1" width="11.28515625" style="4" customWidth="1"/>
+    <col min="2" max="16" width="9.85546875" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="14">
+    <row r="1" spans="1:16" ht="15">
       <c r="A1" s="106" t="s">
         <v>76</v>
       </c>
@@ -1802,7 +1802,7 @@
       <c r="O2" s="96"/>
       <c r="P2" s="96"/>
     </row>
-    <row r="3" spans="1:16" ht="11">
+    <row r="3" spans="1:16" ht="9">
       <c r="A3" s="97" t="s">
         <v>75</v>
       </c>
@@ -1844,7 +1844,7 @@
       <c r="O4" s="108"/>
       <c r="P4" s="109"/>
     </row>
-    <row r="5" spans="1:16" ht="11">
+    <row r="5" spans="1:16" ht="9">
       <c r="A5" s="79"/>
       <c r="B5" s="110" t="s">
         <v>73</v>
@@ -1872,7 +1872,7 @@
       <c r="O5" s="111"/>
       <c r="P5" s="114"/>
     </row>
-    <row r="6" spans="1:16" ht="11">
+    <row r="6" spans="1:16" ht="9">
       <c r="A6" s="79" t="s">
         <v>68</v>
       </c>
@@ -1900,7 +1900,7 @@
       <c r="O6" s="88"/>
       <c r="P6" s="87"/>
     </row>
-    <row r="7" spans="1:16" ht="11">
+    <row r="7" spans="1:16" ht="9">
       <c r="A7" s="79"/>
       <c r="B7" s="79" t="s">
         <v>63</v>
@@ -1946,7 +1946,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="11">
+    <row r="8" spans="1:16" ht="9">
       <c r="A8" s="79"/>
       <c r="B8" s="79" t="s">
         <v>65</v>
@@ -1994,7 +1994,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="11">
+    <row r="9" spans="1:16" ht="9">
       <c r="A9" s="74"/>
       <c r="B9" s="74" t="s">
         <v>60</v>
@@ -2034,7 +2034,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="11">
+    <row r="10" spans="1:16" ht="9">
       <c r="A10" s="19" t="s">
         <v>58</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>5320340</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="11">
+    <row r="11" spans="1:16" ht="9">
       <c r="A11" s="19" t="s">
         <v>57</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>792826</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="11">
+    <row r="12" spans="1:16" ht="9">
       <c r="A12" s="19" t="s">
         <v>56</v>
       </c>
@@ -2184,7 +2184,7 @@
         <v>6053781</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="11">
+    <row r="13" spans="1:16" ht="9">
       <c r="A13" s="19" t="s">
         <v>55</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>2913369</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="11">
+    <row r="14" spans="1:16" ht="9">
       <c r="A14" s="52" t="s">
         <v>54</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>30398249</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="11">
+    <row r="15" spans="1:16" ht="9">
       <c r="A15" s="19" t="s">
         <v>53</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>5350708</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="11">
+    <row r="16" spans="1:16" ht="9">
       <c r="A16" s="19" t="s">
         <v>52</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>2867554</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="11">
+    <row r="17" spans="1:16" ht="9">
       <c r="A17" s="43" t="s">
         <v>51</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>1006135</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="11">
+    <row r="18" spans="1:16" ht="9">
       <c r="A18" s="19" t="s">
         <v>50</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>356537</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="11">
+    <row r="19" spans="1:16" ht="9">
       <c r="A19" s="19" t="s">
         <v>49</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>18464506</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="11">
+    <row r="20" spans="1:16" ht="9">
       <c r="A20" s="19" t="s">
         <v>48</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>8829596</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="11">
+    <row r="21" spans="1:16" ht="9">
       <c r="A21" s="19" t="s">
         <v>47</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>1244935</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="11">
+    <row r="22" spans="1:16" ht="9">
       <c r="A22" s="52" t="s">
         <v>46</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>1917677</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="11">
+    <row r="23" spans="1:16" ht="9">
       <c r="A23" s="19" t="s">
         <v>45</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>10587725</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="11">
+    <row r="24" spans="1:16" ht="9">
       <c r="A24" s="19" t="s">
         <v>44</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>6199901</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="11">
+    <row r="25" spans="1:16" ht="9">
       <c r="A25" s="43" t="s">
         <v>43</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>3787224</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="11">
+    <row r="26" spans="1:16" ht="9">
       <c r="A26" s="19" t="s">
         <v>42</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>2603543</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="11">
+    <row r="27" spans="1:16" ht="9">
       <c r="A27" s="19" t="s">
         <v>41</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>4459685</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="11">
+    <row r="28" spans="1:16" ht="9">
       <c r="A28" s="19" t="s">
         <v>40</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>3861204</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="11">
+    <row r="29" spans="1:16" ht="9">
       <c r="A29" s="19" t="s">
         <v>39</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>1121106</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="11">
+    <row r="30" spans="1:16" ht="9">
       <c r="A30" s="52" t="s">
         <v>38</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>4211377</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="11">
+    <row r="31" spans="1:16" ht="9">
       <c r="A31" s="19" t="s">
         <v>37</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>5036686</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="11">
+    <row r="32" spans="1:16" ht="9">
       <c r="A32" s="19" t="s">
         <v>36</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>8453239</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="11">
+    <row r="33" spans="1:16" ht="9">
       <c r="A33" s="43" t="s">
         <v>35</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>5690749</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="11">
+    <row r="34" spans="1:16" ht="9">
       <c r="A34" s="19" t="s">
         <v>34</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>2058975</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="11">
+    <row r="35" spans="1:16" ht="9">
       <c r="A35" s="19" t="s">
         <v>33</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>5587022</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="11">
+    <row r="36" spans="1:16" ht="9">
       <c r="A36" s="19" t="s">
         <v>32</v>
       </c>
@@ -3384,7 +3384,7 @@
         <v>1952553</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="11">
+    <row r="37" spans="1:16" ht="9">
       <c r="A37" s="19" t="s">
         <v>31</v>
       </c>
@@ -3434,7 +3434,7 @@
         <v>1935357</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="11">
+    <row r="38" spans="1:16" ht="9">
       <c r="A38" s="52" t="s">
         <v>30</v>
       </c>
@@ -3484,7 +3484,7 @@
         <v>2549357</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="11">
+    <row r="39" spans="1:16" ht="9">
       <c r="A39" s="19" t="s">
         <v>29</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>1357535</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="11">
+    <row r="40" spans="1:16" ht="9">
       <c r="A40" s="19" t="s">
         <v>28</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>6006247</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="11">
+    <row r="41" spans="1:16" ht="9">
       <c r="A41" s="43" t="s">
         <v>27</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>1783151</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="11">
+    <row r="42" spans="1:16" ht="9">
       <c r="A42" s="19" t="s">
         <v>26</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>11324755</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="11">
+    <row r="43" spans="1:16" ht="9">
       <c r="A43" s="19" t="s">
         <v>25</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>8739280</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="11">
+    <row r="44" spans="1:16" ht="9">
       <c r="A44" s="19" t="s">
         <v>24</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>899083</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="11">
+    <row r="45" spans="1:16" ht="9">
       <c r="A45" s="19" t="s">
         <v>23</v>
       </c>
@@ -3834,7 +3834,7 @@
         <v>10592317</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="11">
+    <row r="46" spans="1:16" ht="9">
       <c r="A46" s="52" t="s">
         <v>22</v>
       </c>
@@ -3884,7 +3884,7 @@
         <v>3730247</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="11">
+    <row r="47" spans="1:16" ht="9">
       <c r="A47" s="19" t="s">
         <v>21</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>4095442</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="11">
+    <row r="48" spans="1:16" ht="9">
       <c r="A48" s="19" t="s">
         <v>20</v>
       </c>
@@ -3984,7 +3984,7 @@
         <v>10690187</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="11">
+    <row r="49" spans="1:16" ht="9">
       <c r="A49" s="43" t="s">
         <v>19</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>866625</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="11">
+    <row r="50" spans="1:16" ht="9">
       <c r="A50" s="19" t="s">
         <v>18</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>4561299</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="11">
+    <row r="51" spans="1:16" ht="9">
       <c r="A51" s="19" t="s">
         <v>17</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>1294282</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="11">
+    <row r="52" spans="1:16" ht="9">
       <c r="A52" s="19" t="s">
         <v>16</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>5855373</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="11">
+    <row r="53" spans="1:16" ht="9">
       <c r="A53" s="19" t="s">
         <v>15</v>
       </c>
@@ -4234,7 +4234,7 @@
         <v>22419490</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="11">
+    <row r="54" spans="1:16" ht="9">
       <c r="A54" s="52" t="s">
         <v>14</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>2479604</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="11">
+    <row r="55" spans="1:16" ht="9">
       <c r="A55" s="19" t="s">
         <v>13</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>607890</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="11">
+    <row r="56" spans="1:16" ht="9">
       <c r="A56" s="19" t="s">
         <v>12</v>
       </c>
@@ -4384,7 +4384,7 @@
         <v>7606452</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="11">
+    <row r="57" spans="1:16" ht="9">
       <c r="A57" s="43" t="s">
         <v>11</v>
       </c>
@@ -4434,7 +4434,7 @@
         <v>7257401</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="11">
+    <row r="58" spans="1:16" ht="9">
       <c r="A58" s="19" t="s">
         <v>10</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>1657362</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="11">
+    <row r="59" spans="1:16" ht="9">
       <c r="A59" s="19" t="s">
         <v>9</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>5616271</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="11">
+    <row r="60" spans="1:16" ht="9">
       <c r="A60" s="19" t="s">
         <v>8</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>861028</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="11">
+    <row r="61" spans="1:16" ht="9">
       <c r="A61" s="11" t="s">
         <v>7</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>275913237</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="11">
+    <row r="62" spans="1:16" ht="9">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -4652,7 +4652,7 @@
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
     </row>
-    <row r="63" spans="1:16" ht="39.5" customHeight="1">
+    <row r="63" spans="1:16" ht="39.6" customHeight="1">
       <c r="A63" s="105" t="s">
         <v>6</v>
       </c>
@@ -4724,10 +4724,10 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.6640625" customWidth="1"/>
+    <col min="2" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6145,10 +6145,10 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.6640625" customWidth="1"/>
+    <col min="2" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
